--- a/ozone/multistate/ozone_VTZP_MS_1_90_10_split_SHAP.xlsx
+++ b/ozone/multistate/ozone_VTZP_MS_1_90_10_split_SHAP.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0009314120380915221</v>
+        <v>0.000954898941933809</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0004612837475388883</v>
+        <v>0.0004558261873130815</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0004529496093341718</v>
+        <v>0.0004456194732260766</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0004430853499693217</v>
+        <v>0.0004306660103948023</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0003722321545110102</v>
+        <v>0.0003787328877059687</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0003586460433118396</v>
+        <v>0.0003705816478197874</v>
       </c>
     </row>
     <row r="8">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.000355901951318092</v>
+        <v>0.0003499032077756984</v>
       </c>
     </row>
     <row r="9">
@@ -541,33 +541,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003110081021897664</v>
+        <v>0.0002965007884662012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$type_2$</t>
+          <t>$(F_{r}^{\text{SCF}})_{3}$</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0002781918509337932</v>
+        <v>0.0002788738846889116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{3}$</t>
+          <t>$type_2$</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002743539940762484</v>
+        <v>0.0002615294776872879</v>
       </c>
     </row>
     <row r="12">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0002417575772674941</v>
+        <v>0.0002514508726438747</v>
       </c>
     </row>
     <row r="13">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0002403021393907039</v>
+        <v>0.0002398719296756347</v>
       </c>
     </row>
     <row r="14">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0002333792236459747</v>
+        <v>0.0002343266409977061</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0002327113436884962</v>
+        <v>0.0002342846210627771</v>
       </c>
     </row>
     <row r="16">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0002164033118617087</v>
+        <v>0.0002179950362933328</v>
       </c>
     </row>
     <row r="17">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0001989504026806342</v>
+        <v>0.0001950805111340059</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0001641249223189945</v>
+        <v>0.0001567351787066167</v>
       </c>
     </row>
     <row r="19">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0001570902528352561</v>
+        <v>0.0001540711365464228</v>
       </c>
     </row>
     <row r="20">
@@ -684,33 +684,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0001546167443257051</v>
+        <v>0.0001508836710243999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{2}$</t>
+          <t>(h$_{p}$)$_{3}$</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0001395385245896821</v>
+        <v>0.0001370989015990202</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{3}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0001374895199098979</v>
+        <v>0.0001356815201154797</v>
       </c>
     </row>
     <row r="23">
@@ -723,33 +723,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001306568927038188</v>
+        <v>0.0001297768305550863</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$F_{s}$</t>
+          <t>$\langle ss \vert ss \rangle$</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001212135485391163</v>
+        <v>0.0001206377366427882</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$\langle ss \vert ss \rangle$</t>
+          <t>$F_{s}$</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001201986158568187</v>
+        <v>0.0001145287937202707</v>
       </c>
     </row>
     <row r="26">
@@ -762,59 +762,59 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001152944665535944</v>
+        <v>0.000107441338986887</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$(F_{p})_{2}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{3}$</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001074455165375857</v>
+        <v>0.000106282718333243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{3}$</t>
+          <t>$(F_{p})_{2}$</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0001053322311927771</v>
+        <v>0.0001016478244186293</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{2}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9.474974101508241e-05</v>
+        <v>9.762602085995729e-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{3}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.292324888570263e-05</v>
+        <v>9.704408142626161e-05</v>
       </c>
     </row>
     <row r="31">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8.148159869482931e-05</v>
+        <v>9.451872934579576e-05</v>
       </c>
     </row>
     <row r="32">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.11232923353385e-05</v>
+        <v>7.565950209179144e-05</v>
       </c>
     </row>
     <row r="33">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.102840173705652e-05</v>
+        <v>6.864908452315466e-05</v>
       </c>
     </row>
     <row r="34">
@@ -866,111 +866,111 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.544069358164021e-05</v>
+        <v>6.699666127115068e-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{2}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.460115007387419e-05</v>
+        <v>5.964082838099725e-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{3}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6.302493624989628e-05</v>
+        <v>5.820794856354096e-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{2}$</t>
+          <t>(h$_{pq}$)$_{1}$</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.613216481198576e-05</v>
+        <v>5.814513057680332e-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{1}$</t>
+          <t>(h$_{p}$)$_{2}$</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5.544541901269834e-05</v>
+        <v>5.472011505644047e-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{1}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.328051964399939e-05</v>
+        <v>5.359695023326029e-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{0}$</t>
+          <t>(h$_{p}$)$_{1}$</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.267303859173021e-05</v>
+        <v>5.312812382912803e-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>$type_1$</t>
+          <t>$(\eta_{r})_{1}$</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.632558988795879e-05</v>
+        <v>4.564954473911921e-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{1}$</t>
+          <t>$type_1$</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.369895658317284e-05</v>
+        <v>4.514668545021491e-05</v>
       </c>
     </row>
     <row r="43">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.829693505405437e-05</v>
+        <v>4.07794790971672e-05</v>
       </c>
     </row>
     <row r="44">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.241907296894978e-05</v>
+        <v>3.319856396801503e-05</v>
       </c>
     </row>
     <row r="45">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.17338988750487e-05</v>
+        <v>3.11643781256894e-05</v>
       </c>
     </row>
     <row r="46">
@@ -1022,20 +1022,20 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.694067506217311e-05</v>
+        <v>2.60992849459132e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{0}$</t>
+          <t>(h$_{r}$)$_{1}$</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.436547256910575e-05</v>
+        <v>2.492357448098151e-05</v>
       </c>
     </row>
     <row r="48">
@@ -1048,137 +1048,137 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.35314423507103e-05</v>
+        <v>2.459893141530777e-05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{1}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{0}$</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.156208563729692e-05</v>
+        <v>2.198435470824725e-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>$(F_{p})_{3}$</t>
+          <t>(h$_{r}$)$_{0}$</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.076856299642905e-05</v>
+        <v>2.076720436297363e-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{0}$</t>
+          <t>(h$_{rs}$)$_{2}$</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.978708112990365e-05</v>
+        <v>1.984358809638285e-05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{2}$</t>
+          <t>$(F_{p})_{3}$</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.871535748819193e-05</v>
+        <v>1.845448719629642e-05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{2}$</t>
+          <t>$(F_{r})_{3}$</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.674254214806276e-05</v>
+        <v>1.631116481786645e-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{0}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{1}$</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.574881778628747e-05</v>
+        <v>1.525183728363287e-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{3}$</t>
+          <t>$(\eta_{r})_{2}$</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.522080450968379e-05</v>
+        <v>1.489349042821086e-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>$(F_{r})_{3}$</t>
+          <t>(h$_{pr}$)$_{0}$</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.513101101819554e-05</v>
+        <v>1.484281955992587e-05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{1}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.502946943543304e-05</v>
+        <v>1.392472459472376e-05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{1}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.35722227269289e-05</v>
+        <v>1.375669564482603e-05</v>
       </c>
     </row>
     <row r="59">
@@ -1191,20 +1191,20 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.355999283841053e-05</v>
+        <v>1.137678030612633e-05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{2}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.198825881399071e-05</v>
+        <v>1.122034594401725e-05</v>
       </c>
     </row>
     <row r="61">
@@ -1217,46 +1217,46 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.134285618606053e-05</v>
+        <v>1.12046990689738e-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{2}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.132019423019149e-05</v>
+        <v>1.082000690512058e-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{1}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{0}$</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.099269911498202e-05</v>
+        <v>1.021104189202856e-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.034397051427542e-05</v>
+        <v>1.015039026243825e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1269,124 +1269,124 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9.884302960771561e-06</v>
+        <v>9.754561158152032e-06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{1}$</t>
+          <t>$(\eta_{p})_{3}$</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9.505907417576993e-06</v>
+        <v>9.637166269353276e-06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{0}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6.942762513500877e-06</v>
+        <v>9.45388119706342e-06</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{1}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6.884295576996416e-06</v>
+        <v>8.518092931679522e-06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{2}$</t>
+          <t>$(F_{r})_{2}$</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6.77090892206062e-06</v>
+        <v>8.006666088220061e-06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>$(F_{r})_{2}$</t>
+          <t>(h$_{rs}$)$_{0}$</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6.260481390151849e-06</v>
+        <v>7.483893613804276e-06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{1}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{1}$</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5.861376844717022e-06</v>
+        <v>7.363834833469848e-06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{0}$</t>
+          <t>(h$_{pq}$)$_{2}$</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5.841177819402905e-06</v>
+        <v>6.892895409334179e-06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{0}$</t>
+          <t>$(F_{p})_{1}$</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4.441348943124417e-06</v>
+        <v>5.675085473495389e-06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>$(F_{p})_{1}$</t>
+          <t>(h$_{pr}$)$_{1}$</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4.406917766956935e-06</v>
+        <v>5.617267202208573e-06</v>
       </c>
     </row>
     <row r="75">
@@ -1399,59 +1399,59 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.66170205488308e-06</v>
+        <v>4.120353601826755e-06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{0}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3.473942755534332e-06</v>
+        <v>3.618046041011986e-06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3.273190794040008e-06</v>
+        <v>3.43554950633489e-06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>$(F_{r})_{1}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3.250058609643138e-06</v>
+        <v>3.381692734674756e-06</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{1}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3.138116161815038e-06</v>
+        <v>3.170592656110737e-06</v>
       </c>
     </row>
     <row r="80">
@@ -1464,72 +1464,72 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.931717558965267e-06</v>
+        <v>3.158136162671697e-06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{0}$</t>
+          <t>(h$_{rs}$)$_{1}$</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.557465706078698e-06</v>
+        <v>3.050761586737302e-06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.988934711337114e-06</v>
+        <v>2.991871934958175e-06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{1}$</t>
+          <t>$(F_{r})_{1}$</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.819726767721262e-06</v>
+        <v>2.5778053074949e-06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{1}$</t>
+          <t>$(\eta_{p})_{2}$</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.769770875360283e-06</v>
+        <v>2.339679692266389e-06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{2}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.463079153929774e-06</v>
+        <v>2.336123673534576e-06</v>
       </c>
     </row>
     <row r="86">
@@ -1542,98 +1542,98 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.336406988113436e-06</v>
+        <v>1.88302221799686e-06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{0}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.042847185705067e-06</v>
+        <v>1.779258213540509e-06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.040021860056284e-06</v>
+        <v>1.66623661238016e-06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>$(F_{p})_{0}$</t>
+          <t>(h$_{pq}$)$_{0}$</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.011385367132465e-07</v>
+        <v>1.093153412468095e-06</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{0}$</t>
+          <t>$(\eta_{p})_{1}$</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2.748385288514677e-07</v>
+        <v>9.461303651341392e-07</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{1}$</t>
+          <t>$(\eta_{r})_{0}$</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5.285798714218254e-08</v>
+        <v>4.256374927059887e-07</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{1}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3.950984136908857e-08</v>
+        <v>3.036601659421109e-07</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{3}$</t>
+          <t>$(F_{p})_{0}$</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3.921873917609198e-08</v>
+        <v>2.012366051036748e-07</v>
       </c>
     </row>
     <row r="94">
@@ -1646,124 +1646,124 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3.524125272494505e-08</v>
+        <v>2.925922893503355e-08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{1}$</t>
+          <t>$(\eta_{p})_{0}$</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3.157855789155035e-08</v>
+        <v>2.813985502128582e-08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{0}$</t>
+          <t>$(\omega_{r})_{3}$</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2.903522198668069e-08</v>
+        <v>2.298738339691742e-08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{0}$</t>
+          <t>$(\omega_{r})_{1}$</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2.704685081562386e-08</v>
+        <v>2.058724735761464e-08</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{2}$</t>
+          <t>$(\omega_{r})_{0}$</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2.663523857548433e-08</v>
+        <v>1.902842823037762e-08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{3}$</t>
+          <t>$(\omega_{p})_{3}$</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2.396023251038028e-08</v>
+        <v>1.590564297828821e-08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{3}$</t>
+          <t>$(\omega_{p})_{2}$</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.457708989501941e-08</v>
+        <v>1.416929405713835e-08</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>$\mathbf{b}$</t>
+          <t>$(\omega_{p})_{0}$</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.310978595269122e-08</v>
+        <v>1.19723955206267e-08</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{0}$</t>
+          <t>$(\omega_{p})_{1}$</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.02124551414623e-08</v>
+        <v>5.283702319621254e-09</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{2}$</t>
+          <t>$\mathbf{b}$</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6.949597068669247e-09</v>
+        <v>2.964478812583563e-09</v>
       </c>
     </row>
   </sheetData>
